--- a/e2e/expectedData/tunjangan_jabatan_2_Q1.xlsx
+++ b/e2e/expectedData/tunjangan_jabatan_2_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -56,64 +56,73 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>HELENA</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>121,00</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>300,00</t>
+  </si>
+  <si>
+    <t>0000002</t>
+  </si>
+  <si>
+    <t>Syifa Hadju</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>6,00</t>
+  </si>
+  <si>
+    <t>18,00</t>
+  </si>
+  <si>
     <t>HERU YULIANTO</t>
   </si>
   <si>
-    <t>II</t>
-  </si>
-  <si>
     <t>Homestaff</t>
   </si>
   <si>
     <t>400,00</t>
   </si>
   <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>HELENA</t>
-  </si>
-  <si>
-    <t>121,00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>300,00</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>6,00</t>
-  </si>
-  <si>
-    <t>18,00</t>
+    <t>250,00</t>
+  </si>
+  <si>
+    <t>900,00</t>
+  </si>
+  <si>
+    <t>90,00</t>
   </si>
   <si>
     <t>GRAND TOTAL</t>
   </si>
   <si>
-    <t>839,00</t>
-  </si>
-  <si>
-    <t>DILI, 26 August 2026</t>
+    <t>1.339,00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -559,8 +568,8 @@
     <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="6.998" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -625,7 +634,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="3">
-        <v>74003</v>
+        <v>84016</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>13</v>
@@ -633,111 +642,111 @@
       <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="3">
-        <v>84016</v>
+        <v>92003</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3">
+        <v>74003</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="3">
-        <v>92003</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -746,10 +755,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -757,19 +766,19 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -778,11 +787,11 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15"/>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:9" customHeight="1" ht="37.5">
@@ -792,20 +801,20 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D17"/>
       <c r="G17" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D18"/>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/tunjangan_jabatan_2_Q1.xlsx
+++ b/e2e/expectedData/tunjangan_jabatan_2_Q1.xlsx
@@ -122,7 +122,7 @@
     <t>1.339,00</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
